--- a/data/trans_dic/P40_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P40_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>28,66; 34,35</t>
+          <t>28,66; 34,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,65; 37,21</t>
+          <t>30,52; 37,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>29,86; 36,61</t>
+          <t>29,79; 36,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,28; 45,36</t>
+          <t>35,44; 43,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>44,13; 49,64</t>
+          <t>44,21; 49,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,57; 50,22</t>
+          <t>44,34; 50,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,76; 51,23</t>
+          <t>44,76; 51,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>54,14; 59,82</t>
+          <t>53,63; 59,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>37,99; 42,06</t>
+          <t>38,25; 42,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39,66; 43,95</t>
+          <t>39,68; 43,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,08; 43,86</t>
+          <t>39,05; 43,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,97; 52,8</t>
+          <t>46,98; 51,56</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,25%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 10,36</t>
+          <t>7,42; 10,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 12,06</t>
+          <t>9,14; 12,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,51</t>
+          <t>10,55; 13,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 16,63</t>
+          <t>13,94; 16,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,86; 19,63</t>
+          <t>15,64; 19,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,32; 17,95</t>
+          <t>14,18; 17,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,06; 19,58</t>
+          <t>16,0; 19,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,62; 28,97</t>
+          <t>19,58; 22,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,95; 14,3</t>
+          <t>11,95; 14,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,0; 14,37</t>
+          <t>12,06; 14,39</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13,76; 16,12</t>
+          <t>13,76; 16,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,78; 21,96</t>
+          <t>17,14; 19,33</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,5</t>
+          <t>6,48; 11,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 11,55</t>
+          <t>5,57; 11,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,3; 11,3</t>
+          <t>5,98; 11,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,08; 15,41</t>
+          <t>9,68; 14,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11,51; 17,68</t>
+          <t>11,28; 18,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 12,37</t>
+          <t>6,36; 12,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,76; 13,36</t>
+          <t>7,74; 13,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,56; 16,06</t>
+          <t>12,14; 16,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,49; 13,47</t>
+          <t>9,52; 13,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,6</t>
+          <t>6,57; 10,66</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,78; 11,34</t>
+          <t>7,53; 11,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 14,82</t>
+          <t>11,65; 14,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14,71; 17,33</t>
+          <t>14,75; 17,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,59; 18,34</t>
+          <t>15,56; 18,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,81; 17,4</t>
+          <t>14,83; 17,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,02; 19,85</t>
+          <t>17,46; 20,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,93; 30,15</t>
+          <t>27,01; 30,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,34; 28,57</t>
+          <t>25,45; 28,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,71; 26,88</t>
+          <t>23,62; 26,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23,31; 31,07</t>
+          <t>26,27; 28,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>21,4; 23,37</t>
+          <t>21,3; 23,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21,04; 23,04</t>
+          <t>20,98; 23,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19,75; 21,73</t>
+          <t>19,64; 21,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>19,81; 25,04</t>
+          <t>22,28; 24,17</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud regular, malo o muy malo (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es regular, mala o muy mala (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>211289</t>
+          <t>225791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>430146</t>
+          <t>463826</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>641435</t>
+          <t>689617</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>295388; 354067</t>
+          <t>295424; 354751</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>296284; 359687</t>
+          <t>295022; 358252</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>222651; 272914</t>
+          <t>222103; 273734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191944; 233556</t>
+          <t>205057; 249065</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>579514; 651956</t>
+          <t>580632; 653480</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>594547; 669873</t>
+          <t>591463; 669634</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>442758; 506726</t>
+          <t>442751; 509517</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>409009; 451942</t>
+          <t>440853; 485847</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>890600; 985826</t>
+          <t>896701; 984515</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>912358; 1011143</t>
+          <t>912803; 1008535</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>677959; 760816</t>
+          <t>677423; 762200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>609477; 670819</t>
+          <t>657953; 722094</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327411</t>
+          <t>345971</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>480450</t>
+          <t>457274</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>807861</t>
+          <t>803245</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>127219; 175227</t>
+          <t>125577; 173071</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>176872; 232747</t>
+          <t>176446; 233275</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217031; 279284</t>
+          <t>218102; 277977</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>224185; 380984</t>
+          <t>310956; 376655</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>251754; 311589</t>
+          <t>248342; 310168</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>249360; 312452</t>
+          <t>246777; 308632</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>316317; 385628</t>
+          <t>315139; 385318</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>371978; 648197</t>
+          <t>425191; 492254</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>391826; 468857</t>
+          <t>391713; 473971</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>440399; 527712</t>
+          <t>442906; 528388</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>555306; 650783</t>
+          <t>555301; 647353</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>669058; 994475</t>
+          <t>754351; 850852</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80564</t>
+          <t>86766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90397</t>
+          <t>104330</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>170961</t>
+          <t>191096</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>35859; 63401</t>
+          <t>35704; 64090</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27250; 55270</t>
+          <t>26631; 53484</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34329; 61577</t>
+          <t>32569; 60548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65204; 99629</t>
+          <t>68872; 105411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>54822; 84234</t>
+          <t>53718; 86087</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>28682; 56425</t>
+          <t>29000; 55473</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42136; 72566</t>
+          <t>42066; 73538</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>76329; 106055</t>
+          <t>89215; 123092</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97528; 138412</t>
+          <t>97828; 138868</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>60849; 99094</t>
+          <t>61356; 99630</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>84711; 123389</t>
+          <t>81902; 123546</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>149208; 193729</t>
+          <t>168461; 215504</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>619265</t>
+          <t>658528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1000993</t>
+          <t>1025430</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1620257</t>
+          <t>1683958</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>481701; 567352</t>
+          <t>483004; 563588</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>526082; 618946</t>
+          <t>525086; 613680</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>497115; 584215</t>
+          <t>497990; 587180</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>483924; 685249</t>
+          <t>614831; 706844</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>909699; 1018360</t>
+          <t>912314; 1019541</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>894900; 1008834</t>
+          <t>898786; 1010372</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>830297; 941218</t>
+          <t>827297; 935813</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>851747; 1135160</t>
+          <t>979250; 1072353</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1423286; 1554451</t>
+          <t>1416684; 1557011</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1453344; 1591317</t>
+          <t>1449175; 1593972</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1354673; 1490367</t>
+          <t>1347426; 1489535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1407968; 1779452</t>
+          <t>1615114; 1752328</t>
         </is>
       </c>
     </row>
